--- a/docs/tables/UncertaintyGrid.xlsx
+++ b/docs/tables/UncertaintyGrid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Use\GitHub\MSE_TROPIC_ICCAT\docs\TechSpec\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Use\GitHub\MSE_TROPIC_ICCAT\docs\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84175DDC-C41C-4EFE-B889-0EDC9BA3BE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC126ABD-FC02-4462-A0FF-14CCB33E2521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F575133F-8F98-4877-BCFA-9EEBB9E7CC4A}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="20098" windowHeight="10671" xr2:uid="{F575133F-8F98-4877-BCFA-9EEBB9E7CC4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,15 +38,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
-    <t>Maximum age for natural mortality: 17, 20, 25</t>
-  </si>
-  <si>
     <t>Steepness: 0.7, 0.8, 0.9</t>
   </si>
   <si>
-    <t>sigmaR: 0.2, 0.4, 0.6</t>
-  </si>
-  <si>
     <t>Stock</t>
   </si>
   <si>
@@ -83,15 +77,9 @@
     <t>Code</t>
   </si>
   <si>
-    <t>M17, M20, M25</t>
-  </si>
-  <si>
     <t>h0.7, h0.8, h0.9</t>
   </si>
   <si>
-    <t>sigmaR0.2, sigmaR0.4, sigmaR 0.6</t>
-  </si>
-  <si>
     <t>noPS, noBuoy</t>
   </si>
   <si>
@@ -104,7 +92,19 @@
     <t>h07, h08, h09</t>
   </si>
   <si>
-    <t>Inclusion of index: acoustic buoy, PSFAD catch and effort</t>
+    <t>Average natural mortality for adults: 0.26, 0.32, 0.39</t>
+  </si>
+  <si>
+    <t>M0.26, M0.32, M0.39</t>
+  </si>
+  <si>
+    <t>BAI, PS</t>
+  </si>
+  <si>
+    <t>Index of abundance: echosounder buoys (BAI) or catch/effort PSLS</t>
+  </si>
+  <si>
+    <t>Index of abundance: acoustic buoy or PSFAD catch and effort</t>
   </si>
 </sst>
 </file>
@@ -487,128 +487,128 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
